--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>גל חייק - מכתב פרידה</v>
+        <v>עידו כנפי - לחזור למוטב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411119&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411126&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-30</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>גל חייק - מכתב פרידה</v>
+        <v>עידו כנפי - לחזור למוטב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>בן-אל - פתאום נעלמת</v>
+        <v>מענדי וויס - להודות</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411117&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411125&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-30</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>בן-אל - פתאום נעלמת</v>
+        <v>מענדי וויס - להודות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אמיתי צדוק - כיוון אחד</v>
+        <v>מלכה בי - פרא אדם</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411116&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411124&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-30</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אמיתי צדוק - כיוון אחד</v>
+        <v>מלכה בי - פרא אדם</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אלחנן אלחדד &amp; קובי ברומר - אנעים זמירות</v>
+        <v>ישי סיידוף - הרי הקסטל</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411115&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411123&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-30</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אלחנן אלחדד &amp; קובי ברומר - אנעים זמירות</v>
+        <v>ישי סיידוף - הרי הקסטל</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אלחי מידני - שכחתי לחייך</v>
+        <v>יוסף חיים בוסקילה - אשא עיניי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411114&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411122&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-30</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אלחי מידני - שכחתי לחייך</v>
+        <v>יוסף חיים בוסקילה - אשא עיניי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>איתי כהן - אל תדאגי לי</v>
+        <v>היוצרים - מחווה לקלאסיקות - מחרוזת יוונית 2026</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411113&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411121&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-30</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>איתי כהן - אל תדאגי לי</v>
+        <v>היוצרים - מחווה לקלאסיקות - מחרוזת יוונית 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Kaan Ates - Sen Ve Ben (Bedal)</v>
+        <v>היוצרים - מחווה לקלאסיקות - מחרוזת זוהר ארגוב 2026</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411112&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411120&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-30</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Kaan Ates - Sen Ve Ben (Bedal)</v>
+        <v>היוצרים - מחווה לקלאסיקות - מחרוזת זוהר ארגוב 2026</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עידו כנפי - לחזור למוטב</v>
+        <v>שלומי שבת &amp; עמיר בניון - היכן אתה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411126&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411136&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עידו כנפי - לחזור למוטב</v>
+        <v>שלומי שבת &amp; עמיר בניון - היכן אתה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מענדי וויס - להודות</v>
+        <v>שחר כהן - מיי לייף</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411125&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411135&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מענדי וויס - להודות</v>
+        <v>שחר כהן - מיי לייף</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מלכה בי - פרא אדם</v>
+        <v>שון שחר - סקסי גירל</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411124&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411134&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מלכה בי - פרא אדם</v>
+        <v>שון שחר - סקסי גירל</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ישי סיידוף - הרי הקסטל</v>
+        <v>ענבל רז - לא כותבת על אקסים</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411123&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411133&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ישי סיידוף - הרי הקסטל</v>
+        <v>ענבל רז - לא כותבת על אקסים</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יוסף חיים בוסקילה - אשא עיניי</v>
+        <v>סאלי - מה ששלי שלי</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411122&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411132&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יוסף חיים בוסקילה - אשא עיניי</v>
+        <v>סאלי - מה ששלי שלי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>היוצרים - מחווה לקלאסיקות - מחרוזת יוונית 2026</v>
+        <v>חיים איפרגן - יום חדש</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411121&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411131&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>היוצרים - מחווה לקלאסיקות - מחרוזת יוונית 2026</v>
+        <v>חיים איפרגן - יום חדש</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>היוצרים - מחווה לקלאסיקות - מחרוזת זוהר ארגוב 2026</v>
+        <v>ארקדי דוכין - תנו לבלון לעוף</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411120&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411130&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,12 +697,126 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>היוצרים - מחווה לקלאסיקות - מחרוזת זוהר ארגוב 2026</v>
+        <v>ארקדי דוכין - תנו לבלון לעוף</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אסאלה - חיים שלי בלב</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411129&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אסאלה - חיים שלי בלב</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אילנה עדני - מאיר לי אותי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411128&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אילנה עדני - מאיר לי אותי</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אביעד סהר - מחרוזת יוסף 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411127&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אביעד סהר - מחרוזת יוסף 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבת &amp; עמיר בניון - היכן אתה</v>
+        <v>ליאם שמואל - דוז פואה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411136&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411147&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבת &amp; עמיר בניון - היכן אתה</v>
+        <v>ליאם שמואל - דוז פואה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שחר כהן - מיי לייף</v>
+        <v>וואן דאן - באדמאן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411135&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411146&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שחר כהן - מיי לייף</v>
+        <v>וואן דאן - באדמאן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שון שחר - סקסי גירל</v>
+        <v>גיא קהלני - פאזל</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411134&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411145&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-31</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שון שחר - סקסי גירל</v>
+        <v>גיא קהלני - פאזל</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ענבל רז - לא כותבת על אקסים</v>
+        <v>שיר גבאי - תרקדי</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411133&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411144&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-31</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ענבל רז - לא כותבת על אקסים</v>
+        <v>שיר גבאי - תרקדי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>סאלי - מה ששלי שלי</v>
+        <v>עדן מאירי - טוב מושך אליו טוב</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411132&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411143&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-31</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>סאלי - מה ששלי שלי</v>
+        <v>עדן מאירי - טוב מושך אליו טוב</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>חיים איפרגן - יום חדש</v>
+        <v>מאיה דדון - ילדה מהפריפריה</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411131&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411142&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-31</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>חיים איפרגן - יום חדש</v>
+        <v>מאיה דדון - ילדה מהפריפריה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ארקדי דוכין - תנו לבלון לעוף</v>
+        <v>יובל דיין - לא להרגיש כלל</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411130&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411141&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-31</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ארקדי דוכין - תנו לבלון לעוף</v>
+        <v>יובל דיין - לא להרגיש כלל</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אסאלה - חיים שלי בלב</v>
+        <v>גל אוקטן - העיר הזאת</v>
       </c>
       <c r="B9" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411129&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411140&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-31</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אסאלה - חיים שלי בלב</v>
+        <v>גל אוקטן - העיר הזאת</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אילנה עדני - מאיר לי אותי</v>
+        <v>גדי אלטמן &amp; מרב סמן טוב - לאט לאט בשקט</v>
       </c>
       <c r="B10" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411128&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411139&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-31</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אילנה עדני - מאיר לי אותי</v>
+        <v>גדי אלטמן &amp; מרב סמן טוב - לאט לאט בשקט</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אביעד סהר - מחרוזת יוסף 2026</v>
+        <v>איתי לוי - מה שקשה להגיד</v>
       </c>
       <c r="B11" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411127&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411138&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-31</v>
@@ -811,12 +811,50 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אביעד סהר - מחרוזת יוסף 2026</v>
+        <v>איתי לוי - מה שקשה להגיד</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבישי אזיקרי - לחיי התחלות חדשות</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411137&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבישי אזיקרי - לחיי התחלות חדשות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>